--- a/batch-2026-12.xlsx
+++ b/batch-2026-12.xlsx
@@ -452,12 +452,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I1. 通過 — Wed-Sat 第 1 人 (Sat 1/4)</t>
+          <t>I1. 通過 — Sat-Tue 第 1 人</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -629,12 +629,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -662,7 +662,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I2. 通過 — Wed-Sat 第 2 人 (Sat 2/4)</t>
+          <t>I2. 通過 — Sat-Tue 第 2 人 (Sat 2/4)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I3. 通過 — Sat-Tue 第 3 人 (Sat 3/4)</t>
+          <t>I3. 未通過 — Sat 3/4 ✓ 但 Mon 3/2 ✗</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>通過</t>
+          <t>未通過 - 已超過上限人數</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I4. 通過 — Sat-Tue 第 4 人 (Sat 4/4)</t>
+          <t>I4. 未通過 — 同 I3 (週末未滿，平日已滿)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>通過</t>
+          <t>未通過 - 已超過上限人數</t>
         </is>
       </c>
     </row>

--- a/batch-2026-12.xlsx
+++ b/batch-2026-12.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,17 +447,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>測試三</t>
+          <t>測試甲</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -467,24 +467,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-12-05 09:00</t>
+          <t>2026-12-01 09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>測試四</t>
+          <t>測試乙</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -494,61 +494,412 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-12-05 10:00</t>
+          <t>2026-12-01 09:10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>測試五</t>
+          <t>測試丙</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4-10天</t>
+          <t>&gt;10天</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-12-05 11:00</t>
+          <t>2026-12-01 09:20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>測試六</t>
+          <t>測試丁</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1-3天</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-12-01 09:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>測試戊</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>2026-12-12</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4-10天</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-12-05 12:00</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1-3天</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-12-01 09:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>測試己</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-12-02 09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>測試庚</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-12-02 09:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>測試辛</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-12-02 09:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>測試壬</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-12-15 18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>測試癸</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-12-15 12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>測試子</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-12-15 06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>測試丑</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-12-20 09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>測試寅</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-12-20 09:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>測試卯</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-12-20 09:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>測試辰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-12-20 09:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>測試巳</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-12-25 09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>測試午</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-12-25 09:10</t>
         </is>
       </c>
     </row>
@@ -563,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,26 +970,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I1. 通過 — Sat-Tue 第 1 人</t>
+          <t>A1. 未通過 — 起日早於 Gate Day（2026-05-02）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>測試三</t>
+          <t>測試甲</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -647,12 +998,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-12-05 09:00</t>
+          <t>2026-12-01 09:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>通過</t>
+          <t>未通過 - 超出可預約範圍</t>
         </is>
       </c>
     </row>
@@ -662,22 +1013,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I2. 通過 — Sat-Tue 第 2 人 (Sat 2/4)</t>
+          <t>B1. 通過 — 4 天剛好下限</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>測試四</t>
+          <t>測試乙</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -690,7 +1041,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-12-05 10:00</t>
+          <t>2026-12-01 09:10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,40 +1056,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I3. 未通過 — Sat 3/4 ✓ 但 Mon 3/2 ✗</t>
+          <t>B2. 未通過 — 11 天 &gt; 上限 10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>測試五</t>
+          <t>測試丙</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4-10天</t>
+          <t>&gt;10天</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-12-05 11:00</t>
+          <t>2026-12-01 09:20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>未通過 - 已超過上限人數</t>
+          <t>未通過 - 預假天數錯誤</t>
         </is>
       </c>
     </row>
@@ -748,40 +1099,639 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I4. 未通過 — 同 I3 (週末未滿，平日已滿)</t>
+          <t>B3. 未通過 — 3 天 &lt; 下限 4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>測試六</t>
+          <t>測試丁</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1-3天</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-12-01 09:30</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>未通過 - 預假天數錯誤</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B4. 未通過 — 迄日早於起日</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>測試戊</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>2026-12-12</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1-3天</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-12-01 09:40</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>未通過 - 預假天數錯誤</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C1. 通過 — 12/14-12/17 第 1 人 (Mon-Thu, 1/2)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>測試己</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4-10天</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-12-05 12:00</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-12-02 09:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>通過</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C2. 通過 — 12/14-12/17 第 2 人 (2/2)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>測試庚</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-12-02 09:10</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>通過</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C3. 未通過 — 12/14-12/17 第 3 人 (額滿)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>測試辛</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-12-02 09:20</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>未通過 - 已超過上限人數</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P1. 未通過 — 最晚送出，輸掉名額</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>測試壬</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-12-15 18:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>未通過 - 已超過上限人數</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P2. 通過 — 次早送出，拿到第 2 名額</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>測試癸</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-12-15 12:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>通過</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P3. 通過 — 最早送出，拿到第 1 名額</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>測試子</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-12-15 06:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>通過</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>W1. 通過 — Sat-Tue 第 1 人 (Sat 1/4)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>測試丑</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-12-20 09:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>通過</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>W2. 通過 — Sat-Tue 第 2 人 (Sat 2/4)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>測試寅</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-12-20 09:10</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>通過</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>W3. 未通過 — Sat 3/4 ✓ 但 Mon-Tue 3/2 ✗</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>測試卯</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-12-20 09:20</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>未通過 - 已超過上限人數</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>W4. 未通過 — 同 W3 (週末未滿，平日已滿)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>測試辰</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-12-20 09:30</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>未通過 - 已超過上限人數</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>E1. 通過 — 跨年至視窗末端 2027-01-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>測試巳</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-12-25 09:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>通過</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>E2. 未通過 — 迄日 2027-01-04 超出視窗</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>測試午</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4-10天</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-12-25 09:10</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>未通過 - 超出可預約範圍</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>選用：上限例外 walkthrough</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1. 在「上限例外」面板新增 2026-12-26 ~ 2026-12-26，上限人數 = 1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2. 清空批次，重新上傳本檔。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3. 預期：W1 仍 通過 (Sat 1/1)；W2/W3/W4 改為 未通過 - 已超過上限人數，</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        而且已滿日改成只列 12/26 (Sat) 而不是 Mon-Tue。</t>
         </is>
       </c>
     </row>
